--- a/scripts/checks/results/HLR_results_14_>1_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_14_>1_lg_families_Famfirst_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E2" t="n">
-        <v>1484</v>
+        <v>1803</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2832518542518089</v>
+        <v>0.2289660427374866</v>
       </c>
       <c r="H2" t="n">
-        <v>586.4622799559509</v>
+        <v>535.4184094840506</v>
       </c>
       <c r="I2" t="n">
-        <v>1.867790180999188e-109</v>
+        <v>6.165311118376326e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>166.4167646289528</v>
+        <v>204.972863262423</v>
       </c>
       <c r="K2" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L2" t="n">
-        <v>65.76627709379278</v>
+        <v>60.86868798411442</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1121406769736879</v>
+        <v>0.113684339025193</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7273505426173328, 'N1ratio-ArgsPreds': -0.20746099596041467}</t>
+          <t>{'const': 0.5718717535467436, 'N1ratio-ArgsPreds': -2.218404205002331}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 9.29807944785156e-161, 'N1ratio-ArgsPreds': 1.867790180997848e-109}</t>
+          <t>{'const': 1.6885341073455672e-165, 'N1ratio-ArgsPreds': 6.1653111183735e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5322141056490415}</t>
+          <t>{'N1ratio-ArgsPreds': -0.478503963136657}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5322141056490425)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4785039631366576)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5322141056490424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47850396313665755)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(28.325185425181004)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.89660427374877)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E3" t="n">
-        <v>1483</v>
+        <v>1802</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2833340197018642</v>
+        <v>0.2289736207052384</v>
       </c>
       <c r="H3" t="n">
-        <v>293.1521537014121</v>
+        <v>267.5722099730518</v>
       </c>
       <c r="I3" t="n">
-        <v>5.216740544525618e-108</v>
+        <v>1.775752614386992e-102</v>
       </c>
       <c r="J3" t="n">
-        <v>166.3976872048344</v>
+        <v>204.9708487237205</v>
       </c>
       <c r="K3" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L3" t="n">
-        <v>32.89267725895557</v>
+        <v>30.43535126140843</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1122034303471574</v>
+        <v>0.1137463089476806</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7244150022829303, 'N1ratio-ArgsPreds': -0.2082249668854036, 'Fam_class': 0.00010307798138135598}</t>
+          <t>{'const': 0.5727928130395785, 'N1ratio-ArgsPreds': -2.2155869992610966, 'Fam_class': -2.6552683270416638e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.699520003685992e-149, 'N1ratio-ArgsPreds': 6.147673017126461e-106, 'Fam_class': 0.6801489037645043}</t>
+          <t>{'const': 2.0561756431361394e-149, 'N1ratio-ArgsPreds': 1.8133660114712908e-99, 'Fam_class': 0.8941434301697844}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5341739733374355, 'Fam_class': 0.009273970638909805}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47789629925416327, 'Fam_class': -0.0028190819687355837}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5249348997645362), 'Fam_class': np.float64(0.010706840429269778)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46929743048082667), 'Fam_class': np.float64(-0.003135015004377424)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5221095374355498), 'Fam_class': np.float64(0.00906451598571646)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4666618947829379), 'Fam_class': np.float64(-0.00275281088193429)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.259836908116377), 'Fam_class': np.float64(0.008216545005530925)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.77733240424018), 'Fam_class': np.float64(0.0007577967751695844)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>8.216545005534925e-05</v>
+        <v>7.577967751859482e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1700253197192259</v>
+        <v>0.01771080504578991</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6801489037645636</v>
+        <v>0.8941434301734381</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E4" t="n">
-        <v>1480</v>
+        <v>1801</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3438200397117536</v>
+        <v>0.2668682982979526</v>
       </c>
       <c r="H4" t="n">
-        <v>155.0957632262547</v>
+        <v>218.5281780971398</v>
       </c>
       <c r="I4" t="n">
-        <v>1.21472196063553e-132</v>
+        <v>6.919535127744501e-121</v>
       </c>
       <c r="J4" t="n">
-        <v>152.3538590972354</v>
+        <v>194.896868848486</v>
       </c>
       <c r="K4" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L4" t="n">
-        <v>15.96583652510203</v>
+        <v>23.64822746601713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1029417966873212</v>
+        <v>0.1082159182945508</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5981575686294935, 'N1ratio-ArgsPreds': -0.20882185823864333, 'Fam_class': -0.000253850667011329, 'latitude': 0.00382909717371041, 'longitude': -2.6015382535658614e-05, 'Macro_class': 0.047902502946424536}</t>
+          <t>{'const': 0.48495142394155644, 'N1ratio-ArgsPreds': -2.207511772190906, 'Fam_class': -0.00017233715523886533, 'Macro_class': 0.0417177500619034}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.886913643270109e-97, 'N1ratio-ArgsPreds': 1.2708412231894904e-100, 'Fam_class': 0.30978029810223984, 'latitude': 2.977518699107421e-14, 'longitude': 0.8148211866374901, 'Macro_class': 1.4621206736498858e-22}</t>
+          <t>{'const': 1.8819765983986162e-99, 'N1ratio-ArgsPreds': 3.4477478512223863e-103, 'Fam_class': 0.3774123439947591, 'Macro_class': 1.6382105968664932e-21}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5357052201930842, 'Fam_class': -0.022839054480713245, 'latitude': 0.1699245519299409, 'longitude': -0.005527057891621753, 'Macro_class': 0.21598150244963432}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47615449397467385, 'Fam_class': -0.01829692923797103, 'Macro_class': 0.19525791362427658}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5137884196152028), 'Fam_class': np.float64(-0.026401283593912573), 'latitude': np.float64(0.1956551665134049), 'longitude': np.float64(-0.00608899671029994), 'Macro_class': np.float64(0.25004775460458567)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47719659536302883), 'Fam_class': np.float64(-0.02079968999636218), 'Macro_class': np.float64(0.22169428095286267)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48512153557829), 'Fam_class': np.float64(-0.021393800127557823), 'latitude': np.float64(0.16161389278881805), 'longitude': np.float64(-0.004932479306975286), 'Macro_class': np.float64(0.20919646107351747)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.464943289129415), 'Fam_class': np.float64(-0.017813195159487066), 'Macro_class': np.float64(0.1946655531744471)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.53429042818381), 'Fam_class': np.float64(0.04576946838978931), 'latitude': np.float64(2.6119050342355576), 'longitude': np.float64(0.0024329352113739403), 'Macro_class': np.float64(4.376315932568371)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.617226210647882), 'Fam_class': np.float64(0.031730992178997344), 'Macro_class': np.float64(3.7894677592713486)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.06048602000988934</v>
+        <v>0.03789467759271414</v>
       </c>
       <c r="V4" t="n">
-        <v>45.47497893479924</v>
+        <v>93.09147890622116</v>
       </c>
       <c r="W4" t="n">
-        <v>4.132125000157097e-28</v>
+        <v>1.638210596866548e-21</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E5" t="n">
-        <v>1478</v>
+        <v>1799</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3534650481512173</v>
+        <v>0.2755305842342348</v>
       </c>
       <c r="H5" t="n">
-        <v>115.4332336610335</v>
+        <v>136.8393227513833</v>
       </c>
       <c r="I5" t="n">
-        <v>3.578062400881211e-135</v>
+        <v>3.617978631520469e-123</v>
       </c>
       <c r="J5" t="n">
-        <v>150.1144517003192</v>
+        <v>192.5940733178437</v>
       </c>
       <c r="K5" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L5" t="n">
-        <v>11.72408428891805</v>
+        <v>14.64949558573874</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1015659348446003</v>
+        <v>0.1070561830560554</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.6458937585888842, 'N1ratio-ArgsPreds': -0.2011464920590777, 'Fam_class': -0.000499043484591848, 'latitude': 0.00392516452114232, 'longitude': -0.0001271014627228238, 'Macro_class': 0.042297027722486426, 'Nlen_freq': -0.05268262244579999, 'Vlen_freq': 0.048073781800680365}</t>
+          <t>{'const': 0.4980467588121561, 'N1ratio-ArgsPreds': -2.1511284754025355, 'Fam_class': -0.00034239971156965965, 'Macro_class': 0.0352278150523109, 'Nlen_freq': -0.44382234741068716, 'Vlen_freq': 0.5743810816477}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 3.7954928616528746e-35, 'N1ratio-ArgsPreds': 2.358589485042511e-92, 'Fam_class': 0.0506886030121392, 'latitude': 5.012573281159711e-15, 'longitude': 0.26156407027062645, 'Macro_class': 3.1576157838923644e-16, 'Nlen_freq': 1.4809540184846323e-05, 'Vlen_freq': 5.002701251435115e-06}</t>
+          <t>{'const': 1.2425434064210297e-53, 'N1ratio-ArgsPreds': 5.82679153564602e-98, 'Fam_class': 0.0859880442851407, 'Macro_class': 4.5258177073381155e-14, 'Nlen_freq': 6.586536210252211e-05, 'Vlen_freq': 4.008430018420185e-06}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5160150701102905, 'Fam_class': -0.044899158497501736, 'latitude': 0.17418775033596284, 'longitude': -0.027003144836173627, 'Macro_class': 0.19070768821565975, 'Nlen_freq': -0.16614374439240992, 'Vlen_freq': 0.18469789822205712}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4639927648780968, 'Fam_class': -0.03635236571596202, 'Macro_class': 0.16488208636490106, 'Nlen_freq': -0.1455617696926089, 'Vlen_freq': 0.17854009193854842}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4950973035761213), 'Fam_class': np.float64(-0.050804707075893005), 'latitude': np.float64(0.20152229650106715), 'longitude': np.float64(-0.029201699213625924), 'Macro_class': np.float64(0.21009867671883617), 'Nlen_freq': np.float64(-0.11233044011965491), 'Vlen_freq': np.float64(0.11833592707351592)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46643005346459615), 'Fam_class': np.float64(-0.04046922026271198), 'Macro_class': np.float64(0.1765108855249669), 'Nlen_freq': np.float64(-0.09389408851483938), 'Vlen_freq': np.float64(0.10840577137066519)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4581925156088449), 'Fam_class': np.float64(-0.0409035651729574), 'latitude': np.float64(0.1654328660103013), 'longitude': np.float64(-0.023490343970052303), 'Macro_class': np.float64(0.17279155274603586), 'Nlen_freq': np.float64(-0.09089728042636723), 'Vlen_freq': np.float64(0.09582413573905645)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44881792886816796), 'Fam_class': np.float64(-0.03447392963613354), 'Macro_class': np.float64(0.15263517026810833), 'Nlen_freq': np.float64(-0.08027330772064811), 'Vlen_freq': np.float64(0.09281740421536674)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.994038135996156), 'Fam_class': np.float64(0.16731016438583737), 'latitude': np.float64(2.7368033156382303), 'longitude': np.float64(0.055179625983137255), 'Macro_class': np.float64(2.985692070038609), 'Nlen_freq': np.float64(0.8262315588909642), 'Vlen_freq': np.float64(0.9182264990137116)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.143753327351188), 'Fam_class': np.float64(0.11884518245570866), 'Macro_class': np.float64(2.329749520277442), 'Nlen_freq': np.float64(0.6443803932413864), 'Vlen_freq': np.float64(0.861507052527878)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.009645008439463698</v>
+        <v>0.008662285936282266</v>
       </c>
       <c r="V5" t="n">
-        <v>11.02440203175706</v>
+        <v>10.75507955218514</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76817099401011e-05</v>
+        <v>2.274216811341173e-05</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_14_>1_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_14_>1_lg_families_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2289660427374866</v>
+        <v>0.2230905752383499</v>
       </c>
       <c r="H2" t="n">
-        <v>535.4184094840506</v>
+        <v>517.7338494485975</v>
       </c>
       <c r="I2" t="n">
-        <v>6.165311118376326e-104</v>
+        <v>5.857522915737756e-101</v>
       </c>
       <c r="J2" t="n">
-        <v>204.972863262423</v>
+        <v>205.036942502581</v>
       </c>
       <c r="K2" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L2" t="n">
-        <v>60.86868798411442</v>
+        <v>58.87663090462121</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113684339025193</v>
+        <v>0.113719879369152</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5718717535467436, 'N1ratio-ArgsPreds': -2.218404205002331}</t>
+          <t>{'const': 0.5587190655100238, 'N1ratio-ArgsPreds': -2.145662524819709}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 1.6885341073455672e-165, 'N1ratio-ArgsPreds': 6.1653111183735e-104}</t>
+          <t>{'const': 3.9637284724572447e-162, 'N1ratio-ArgsPreds': 5.857522915737049e-101}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.478503963136657}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47232465025483217}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4785039631366576)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47232465025483383)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47850396313665755)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723246502548339)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.89660427374877)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.309057523835115)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2289736207052384</v>
+        <v>0.2231248361012059</v>
       </c>
       <c r="H3" t="n">
-        <v>267.5722099730518</v>
+        <v>258.7744938559731</v>
       </c>
       <c r="I3" t="n">
-        <v>1.775752614386992e-102</v>
+        <v>1.608663049382164e-99</v>
       </c>
       <c r="J3" t="n">
-        <v>204.9708487237205</v>
+        <v>205.0279005958367</v>
       </c>
       <c r="K3" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L3" t="n">
-        <v>30.43535126140843</v>
+        <v>29.4428364056828</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1137463089476806</v>
+        <v>0.1137779692540714</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5727928130395785, 'N1ratio-ArgsPreds': -2.2155869992610966, 'Fam_class': -2.6552683270416638e-05}</t>
+          <t>{'const': 0.560702737381192, 'N1ratio-ArgsPreds': -2.139913914280309, 'Fam_class': -5.6200300629350526e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.0561756431361394e-149, 'N1ratio-ArgsPreds': 1.8133660114712908e-99, 'Fam_class': 0.8941434301697844}</t>
+          <t>{'const': 5.5586834044037545e-146, 'N1ratio-ArgsPreds': 1.5706816214764862e-96, 'Fam_class': 0.7780496497473899}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47789629925416327, 'Fam_class': -0.0028190819687355837}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47105920872753443, 'Fam_class': -0.005988506083872777}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46929743048082667), 'Fam_class': np.float64(-0.003135015004377424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4630074102758243), 'Fam_class': np.float64(-0.006640701410264955)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4666618947829379), 'Fam_class': np.float64(-0.00275281088193429)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4604220893989414), 'Fam_class': np.float64(-0.005853277958239459)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.77733240424018), 'Fam_class': np.float64(0.0007577967751695844)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.198850040648683), 'Fam_class': np.float64(0.0034260862856411883)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>7.577967751859482e-06</v>
+        <v>3.426086285607255e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01771080504578991</v>
+        <v>0.0794697497559409</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8941434301734381</v>
+        <v>0.778049649751871</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2668682982979526</v>
+        <v>0.2617402977261597</v>
       </c>
       <c r="H4" t="n">
-        <v>218.5281780971398</v>
+        <v>212.8403120441759</v>
       </c>
       <c r="I4" t="n">
-        <v>6.919535127744501e-121</v>
+        <v>3.646215143978709e-118</v>
       </c>
       <c r="J4" t="n">
-        <v>194.896868848486</v>
+        <v>194.8367561296264</v>
       </c>
       <c r="K4" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L4" t="n">
-        <v>23.64822746601713</v>
+        <v>23.02560575919194</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1082159182945508</v>
+        <v>0.1081825408826354</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.48495142394155644, 'N1ratio-ArgsPreds': -2.207511772190906, 'Fam_class': -0.00017233715523886533, 'Macro_class': 0.0417177500619034}</t>
+          <t>{'const': 0.4720195121064771, 'N1ratio-ArgsPreds': -2.129686796291055, 'Fam_class': -0.0002037412704466695, 'Macro_class': 0.041960675139399314}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.8819765983986162e-99, 'N1ratio-ArgsPreds': 3.4477478512223863e-103, 'Fam_class': 0.3774123439947591, 'Macro_class': 1.6382105968664932e-21}</t>
+          <t>{'const': 8.484546750387404e-96, 'N1ratio-ArgsPreds': 5.302069347401985e-100, 'Fam_class': 0.29621687497335525, 'Macro_class': 9.604855698719625e-22}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47615449397467385, 'Fam_class': -0.01829692923797103, 'Macro_class': 0.19525791362427658}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4688079134415736, 'Fam_class': -0.021709952152260386, 'Macro_class': 0.1971109729301701}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47719659536302883), 'Fam_class': np.float64(-0.02079968999636218), 'Macro_class': np.float64(0.22169428095286267)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47054188077584597), 'Fam_class': np.float64(-0.0246138508046279), 'Macro_class': np.float64(0.22294872685681663)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.464943289129415), 'Fam_class': np.float64(-0.017813195159487066), 'Macro_class': np.float64(0.1946655531744471)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45819290559705006), 'Fam_class': np.float64(-0.021155132127956066), 'Macro_class': np.float64(0.1965081719037516)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.617226210647882), 'Fam_class': np.float64(0.031730992178997344), 'Macro_class': np.float64(3.7894677592713486)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.99407387394672), 'Fam_class': np.float64(0.044753961535127895), 'Macro_class': np.float64(3.861546162495439)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03789467759271414</v>
+        <v>0.03861546162495377</v>
       </c>
       <c r="V4" t="n">
-        <v>93.09147890622116</v>
+        <v>94.20322709249692</v>
       </c>
       <c r="W4" t="n">
-        <v>1.638210596866548e-21</v>
+        <v>9.604855698731341e-22</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2755305842342348</v>
+        <v>0.2717040675328667</v>
       </c>
       <c r="H5" t="n">
-        <v>136.8393227513833</v>
+        <v>134.229945740823</v>
       </c>
       <c r="I5" t="n">
-        <v>3.617978631520469e-123</v>
+        <v>4.048499415195737e-121</v>
       </c>
       <c r="J5" t="n">
-        <v>192.5940733178437</v>
+        <v>192.2071820353316</v>
       </c>
       <c r="K5" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L5" t="n">
-        <v>14.64949558573874</v>
+        <v>14.34127827437413</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1070561830560554</v>
+        <v>0.1068411239773939</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4980467588121561, 'N1ratio-ArgsPreds': -2.1511284754025355, 'Fam_class': -0.00034239971156965965, 'Macro_class': 0.0352278150523109, 'Nlen_freq': -0.44382234741068716, 'Vlen_freq': 0.5743810816477}</t>
+          <t>{'const': 0.4901173108997009, 'N1ratio-ArgsPreds': -2.0734691022880956, 'Fam_class': -0.0003778693762790817, 'Macro_class': 0.03521066658324588, 'Nlen_freq': -0.4814909423293312, 'Vlen_freq': 0.6092779611926796}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 1.2425434064210297e-53, 'N1ratio-ArgsPreds': 5.82679153564602e-98, 'Fam_class': 0.0859880442851407, 'Macro_class': 4.5258177073381155e-14, 'Nlen_freq': 6.586536210252211e-05, 'Vlen_freq': 4.008430018420185e-06}</t>
+          <t>{'const': 2.7913104421383427e-52, 'N1ratio-ArgsPreds': 6.190586659119072e-95, 'Fam_class': 0.057610559733342837, 'Macro_class': 4.245562584459251e-14, 'Nlen_freq': 1.3739064374917081e-05, 'Vlen_freq': 8.90510264621053e-07}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4639927648780968, 'Fam_class': -0.03635236571596202, 'Macro_class': 0.16488208636490106, 'Nlen_freq': -0.1455617696926089, 'Vlen_freq': 0.17854009193854842}</t>
+          <t>{'N1ratio-ArgsPreds': -0.45643271354367165, 'Fam_class': -0.040264429788026974, 'Macro_class': 0.16540269489674322, 'Nlen_freq': -0.15867049025685165, 'Vlen_freq': 0.19035569947453163}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46643005346459615), 'Fam_class': np.float64(-0.04046922026271198), 'Macro_class': np.float64(0.1765108855249669), 'Nlen_freq': np.float64(-0.09389408851483938), 'Vlen_freq': np.float64(0.10840577137066519)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.459874230724859), 'Fam_class': np.float64(-0.04474783222068816), 'Macro_class': np.float64(0.1767026073237232), 'Nlen_freq': np.float64(-0.10225699191183658), 'Vlen_freq': np.float64(0.1154940386856135)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44881792886816796), 'Fam_class': np.float64(-0.03447392963613354), 'Macro_class': np.float64(0.15263517026810833), 'Nlen_freq': np.float64(-0.08027330772064811), 'Vlen_freq': np.float64(0.09281740421536674)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4419649676232452), 'Fam_class': np.float64(-0.038226205303686506), 'Macro_class': np.float64(0.15320931543352032), 'Nlen_freq': np.float64(-0.08772623852018055), 'Vlen_freq': np.float64(0.09922691782955548)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.143753327351188), 'Fam_class': np.float64(0.11884518245570866), 'Macro_class': np.float64(2.329749520277442), 'Nlen_freq': np.float64(0.6443803932413864), 'Vlen_freq': np.float64(0.861507052527878)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.533303260621622), 'Fam_class': np.float64(0.14612427719195903), 'Macro_class': np.float64(2.3473094335607927), 'Nlen_freq': np.float64(0.7695892924899609), 'Vlen_freq': np.float64(0.9845981221953355)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.008662285936282266</v>
+        <v>0.00996376980670699</v>
       </c>
       <c r="V5" t="n">
-        <v>10.75507955218514</v>
+        <v>12.30600164245376</v>
       </c>
       <c r="W5" t="n">
-        <v>2.274216811341173e-05</v>
+        <v>4.918126932642786e-06</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_14_>1_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_14_>1_lg_families_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2230905752383499</v>
+        <v>0.2229212985647023</v>
       </c>
       <c r="H2" t="n">
-        <v>517.7338494485975</v>
+        <v>517.2283072097867</v>
       </c>
       <c r="I2" t="n">
-        <v>5.857522915737756e-101</v>
+        <v>7.131389721807892e-101</v>
       </c>
       <c r="J2" t="n">
-        <v>205.036942502581</v>
+        <v>205.0816169144178</v>
       </c>
       <c r="K2" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L2" t="n">
-        <v>58.87663090462121</v>
+        <v>58.8319564927844</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113719879369152</v>
+        <v>0.1137446571904702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5587190655100238, 'N1ratio-ArgsPreds': -2.145662524819709}</t>
+          <t>{'const': 0.5582554068474909, 'N1ratio-ArgsPreds': -2.1419111097183157}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.9637284724572447e-162, 'N1ratio-ArgsPreds': 5.857522915737049e-101}</t>
+          <t>{'const': 4.624050485653135e-162, 'N1ratio-ArgsPreds': 7.131389721806646e-101}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47232465025483217}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47214542099304796}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47232465025483383)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47214542099304907)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723246502548339)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47214542099304924)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.309057523835115)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.292129856470368)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2231248361012059</v>
+        <v>0.2229547310752517</v>
       </c>
       <c r="H3" t="n">
-        <v>258.7744938559731</v>
+        <v>258.5206045675775</v>
       </c>
       <c r="I3" t="n">
-        <v>1.608663049382164e-99</v>
+        <v>1.959452906202537e-99</v>
       </c>
       <c r="J3" t="n">
-        <v>205.0279005958367</v>
+        <v>205.0727936210907</v>
       </c>
       <c r="K3" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L3" t="n">
-        <v>29.4428364056828</v>
+        <v>29.42038989305573</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1137779692540714</v>
+        <v>0.1138028821426697</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.560702737381192, 'N1ratio-ArgsPreds': -2.139913914280309, 'Fam_class': -5.6200300629350526e-05}</t>
+          <t>{'const': 0.5602148077775055, 'N1ratio-ArgsPreds': -2.1362337844613317, 'Fam_class': -5.5519547741680146e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 5.5586834044037545e-146, 'N1ratio-ArgsPreds': 1.5706816214764862e-96, 'Fam_class': 0.7780496497473899}</t>
+          <t>{'const': 6.8348741435208885e-146, 'N1ratio-ArgsPreds': 1.9139532586621353e-96, 'Fam_class': 0.7807030687217626}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47105920872753443, 'Fam_class': -0.005988506083872777}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47089395770336656, 'Fam_class': -0.005915967453940628}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4630074102758243), 'Fam_class': np.float64(-0.006640701410264955)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46282160846745146), 'Fam_class': np.float64(-0.00655921689850517)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4604220893989414), 'Fam_class': np.float64(-0.005853277958239459)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4602373250623426), 'Fam_class': np.float64(-0.005782085311498247)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.198850040648683), 'Fam_class': np.float64(0.0034260862856411883)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.181839538054042), 'Fam_class': np.float64(0.0033432510549443774)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>3.426086285607255e-05</v>
+        <v>3.343251054932495e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0794697497559409</v>
+        <v>0.07753136968873034</v>
       </c>
       <c r="W3" t="n">
-        <v>0.778049649751871</v>
+        <v>0.7807030687255732</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2617402977261597</v>
+        <v>0.2616068682341255</v>
       </c>
       <c r="H4" t="n">
-        <v>212.8403120441759</v>
+        <v>212.6933695256575</v>
       </c>
       <c r="I4" t="n">
-        <v>3.646215143978709e-118</v>
+        <v>4.289512620978463e-118</v>
       </c>
       <c r="J4" t="n">
-        <v>194.8367561296264</v>
+        <v>194.871969983667</v>
       </c>
       <c r="K4" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L4" t="n">
-        <v>23.02560575919194</v>
+        <v>23.01386780784505</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1081825408826354</v>
+        <v>0.1082020932724414</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4720195121064771, 'N1ratio-ArgsPreds': -2.129686796291055, 'Fam_class': -0.0002037412704466695, 'Macro_class': 0.041960675139399314}</t>
+          <t>{'const': 0.4715194025912685, 'N1ratio-ArgsPreds': -2.1261970725890595, 'Fam_class': -0.00020305575605384697, 'Macro_class': 0.04198050396622711}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 8.484546750387404e-96, 'N1ratio-ArgsPreds': 5.302069347401985e-100, 'Fam_class': 0.29621687497335525, 'Macro_class': 9.604855698719625e-22}</t>
+          <t>{'const': 1.0653031829177924e-95, 'N1ratio-ArgsPreds': 6.241064765797456e-100, 'Fam_class': 0.29791086649887016, 'Macro_class': 9.276610556458838e-22}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4688079134415736, 'Fam_class': -0.021709952152260386, 'Macro_class': 0.1971109729301701}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4686815467723905, 'Fam_class': -0.021636906153110414, 'Macro_class': 0.19720411917567515}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47054188077584597), 'Fam_class': np.float64(-0.0246138508046279), 'Macro_class': np.float64(0.22294872685681663)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4703923287083415), 'Fam_class': np.float64(-0.024527713941786412), 'Macro_class': np.float64(0.22303015987903108)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.45819290559705006), 'Fam_class': np.float64(-0.021155132127956066), 'Macro_class': np.float64(0.1965081719037516)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4580472783975752), 'Fam_class': np.float64(-0.021082959462260426), 'Macro_class': np.float64(0.1966014678451712)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.99407387394672), 'Fam_class': np.float64(0.044753961535127895), 'Macro_class': np.float64(3.861546162495439)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.980730924742577), 'Fam_class': np.float64(0.04444911796873165), 'Macro_class': np.float64(3.865213715887589)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03861546162495377</v>
+        <v>0.03865213715887383</v>
       </c>
       <c r="V4" t="n">
-        <v>94.20322709249692</v>
+        <v>94.27565889819803</v>
       </c>
       <c r="W4" t="n">
-        <v>9.604855698731341e-22</v>
+        <v>9.276610556462387e-22</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2717040675328667</v>
+        <v>0.2715872720337371</v>
       </c>
       <c r="H5" t="n">
-        <v>134.229945740823</v>
+        <v>134.1507317569339</v>
       </c>
       <c r="I5" t="n">
-        <v>4.048499415195737e-121</v>
+        <v>4.673665264680472e-121</v>
       </c>
       <c r="J5" t="n">
-        <v>192.2071820353316</v>
+        <v>192.2380059528647</v>
       </c>
       <c r="K5" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L5" t="n">
-        <v>14.34127827437413</v>
+        <v>14.3351134908675</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1068411239773939</v>
+        <v>0.1068582578948664</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4901173108997009, 'N1ratio-ArgsPreds': -2.0734691022880956, 'Fam_class': -0.0003778693762790817, 'Macro_class': 0.03521066658324588, 'Nlen_freq': -0.4814909423293312, 'Vlen_freq': 0.6092779611926796}</t>
+          <t>{'const': 0.4899926038435314, 'N1ratio-ArgsPreds': -2.069983257552075, 'Fam_class': -0.00037675014764282664, 'Macro_class': 0.0352378824994168, 'Nlen_freq': -0.4890318790396833, 'Vlen_freq': 0.6096321626398418}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 2.7913104421383427e-52, 'N1ratio-ArgsPreds': 6.190586659119072e-95, 'Fam_class': 0.057610559733342837, 'Macro_class': 4.245562584459251e-14, 'Nlen_freq': 1.3739064374917081e-05, 'Vlen_freq': 8.90510264621053e-07}</t>
+          <t>{'const': 2.735078936108381e-52, 'N1ratio-ArgsPreds': 7.542952142368917e-95, 'Fam_class': 0.058388611787834006, 'Macro_class': 4.0810315939871304e-14, 'Nlen_freq': 1.2980441262438497e-05, 'Vlen_freq': 8.828742798608111e-07}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.45643271354367165, 'Fam_class': -0.040264429788026974, 'Macro_class': 0.16540269489674322, 'Nlen_freq': -0.15867049025685165, 'Vlen_freq': 0.19035569947453163}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4562902317239556, 'Fam_class': -0.040145168726744375, 'Macro_class': 0.16553054211792867, 'Nlen_freq': -0.1591912080634069, 'Vlen_freq': 0.19050256423102313}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.459874230724859), 'Fam_class': np.float64(-0.04474783222068816), 'Macro_class': np.float64(0.1767026073237232), 'Nlen_freq': np.float64(-0.10225699191183658), 'Vlen_freq': np.float64(0.1154940386856135)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45968624156691695), 'Fam_class': np.float64(-0.0446093717477114), 'Macro_class': np.float64(0.17682104275351457), 'Nlen_freq': np.float64(-0.10254811473235292), 'Vlen_freq': np.float64(0.1155334211967393)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4419649676232452), 'Fam_class': np.float64(-0.038226205303686506), 'Macro_class': np.float64(0.15320931543352032), 'Nlen_freq': np.float64(-0.08772623852018055), 'Vlen_freq': np.float64(0.09922691782955548)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44177129971872175), 'Fam_class': np.float64(-0.038110743594060734), 'Macro_class': np.float64(0.15332761049202123), 'Nlen_freq': np.float64(-0.08798569744322482), 'Vlen_freq': np.float64(0.09926916990537328)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.533303260621622), 'Fam_class': np.float64(0.14612427719195903), 'Macro_class': np.float64(2.3473094335607927), 'Nlen_freq': np.float64(0.7695892924899609), 'Vlen_freq': np.float64(0.9845981221953355)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.51618812551687), 'Fam_class': np.float64(0.14524287772922412), 'Macro_class': np.float64(2.350935613919298), 'Nlen_freq': np.float64(0.7741482954570699), 'Vlen_freq': np.float64(0.9854368093701869)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.00996376980670699</v>
+        <v>0.009980403799611626</v>
       </c>
       <c r="V5" t="n">
-        <v>12.30600164245376</v>
+        <v>12.32456940011962</v>
       </c>
       <c r="W5" t="n">
-        <v>4.918126932642786e-06</v>
+        <v>4.828861753142112e-06</v>
       </c>
     </row>
   </sheetData>
